--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135675283</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135675359</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135675283</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135675359</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135675283</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135675359</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29898-2026 artfynd.xlsx
+++ b/artfynd/A 29898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135675244</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135675283</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>135675359</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
